--- a/data/trans_orig/P70C2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023</t>
+          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>160874</t>
+          <t>162101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181398</t>
+          <t>181512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114072</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128197</t>
+          <t>128443</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284693</t>
+          <t>284535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306784</t>
+          <t>306691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32070</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>11338</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18840</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1182,97 +1182,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>436</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2247</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2512</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1295,97 +1295,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90091</t>
+          <t>90652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128586</t>
+          <t>131049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58311</t>
+          <t>60256</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82701</t>
+          <t>82939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156270</t>
+          <t>156019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201910</t>
+          <t>201243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>22577</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50974</t>
+          <t>51836</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42212</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76384</t>
+          <t>77021</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54157</t>
+          <t>54160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34488</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69344</t>
+          <t>70145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35888</t>
+          <t>36751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>71517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25323</t>
+          <t>25220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44007</t>
+          <t>43892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68607</t>
+          <t>68700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110419</t>
+          <t>106595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26365</t>
+          <t>27718</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39205</t>
+          <t>39522</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24202</t>
+          <t>26220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45957</t>
+          <t>45784</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69206</t>
+          <t>70165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49398</t>
+          <t>50642</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69450</t>
+          <t>69108</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101634</t>
+          <t>102192</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>131268</t>
+          <t>131986</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44046</t>
+          <t>44355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28372</t>
+          <t>27717</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42243</t>
+          <t>43245</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66653</t>
+          <t>68831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>24951</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45726</t>
+          <t>46091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>23999</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>20240</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>38245</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18693</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35546</t>
+          <t>36089</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74955</t>
+          <t>77353</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109565</t>
+          <t>109615</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132378</t>
+          <t>138769</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>223190</t>
+          <t>220691</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>222569</t>
+          <t>227787</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>340479</t>
+          <t>329707</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>14306</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33971</t>
+          <t>35424</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49447</t>
+          <t>47550</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29163</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73440</t>
+          <t>72818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>31470</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22885</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>42755</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30294</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>36960</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>56125</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21550</t>
+          <t>22392</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>31107</t>
+          <t>31404</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>67041</t>
+          <t>67261</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>83465</t>
+          <t>84365</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>77336</t>
+          <t>77415</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>90109</t>
+          <t>89994</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>148860</t>
+          <t>148667</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>169823</t>
+          <t>169523</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21089</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30243</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>14532</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19226</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>320</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -4475,97 +4475,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>38734</t>
+          <t>38732</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>61108</t>
+          <t>61368</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>30166</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>46032</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>74205</t>
+          <t>73230</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>101337</t>
+          <t>100177</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>28691</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23314</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>28074</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>47654</t>
+          <t>47538</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>21802</t>
+          <t>23021</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>32177</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>51125</t>
+          <t>50821</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>34332</t>
+          <t>34913</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>149473</t>
+          <t>146533</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>189938</t>
+          <t>188900</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>161447</t>
+          <t>161440</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>193002</t>
+          <t>192819</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>319419</t>
+          <t>318891</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>374722</t>
+          <t>373242</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>66883</t>
+          <t>66404</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>108908</t>
+          <t>110721</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>65773</t>
+          <t>66870</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>117942</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>169420</t>
+          <t>170761</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>36561</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>22743</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>28463</t>
+          <t>29068</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>53976</t>
+          <t>54234</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>38001</t>
+          <t>38860</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>17490</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>34141</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>38990</t>
+          <t>37061</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>66280</t>
+          <t>65898</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>28727</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>32093</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>29920</t>
+          <t>28891</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>53157</t>
+          <t>53766</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>18790</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>32761</t>
+          <t>32208</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>306924</t>
+          <t>306923</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>306924</t>
+          <t>306923</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>306924</t>
+          <t>306923</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>314185</t>
+          <t>314493</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>555809</t>
+          <t>549579</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>100613</t>
+          <t>101414</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>129235</t>
+          <t>130678</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>423697</t>
+          <t>420918</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>741138</t>
+          <t>739291</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>47344</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>198568</t>
+          <t>199945</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>68164</t>
+          <t>67359</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>95072</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>92671</t>
+          <t>88145</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>277386</t>
+          <t>278987</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>52420</t>
+          <t>49413</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>28908</t>
+          <t>28819</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>48406</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>94788</t>
+          <t>94777</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>37587</t>
+          <t>36692</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>24415</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>54913</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>29909</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>41443</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>30166</t>
+          <t>30308</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>36833</t>
+          <t>35759</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>973435</t>
+          <t>968866</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1360166</t>
+          <t>1379152</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>714590</t>
+          <t>721708</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>885552</t>
+          <t>883061</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1730046</t>
+          <t>1735249</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2220712</t>
+          <t>2259673</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>273837</t>
+          <t>265924</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>470372</t>
+          <t>473770</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>263452</t>
+          <t>269935</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>352211</t>
+          <t>349112</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>562213</t>
+          <t>559840</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>801082</t>
+          <t>796708</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>97858</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>183324</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>93200</t>
+          <t>91080</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>133419</t>
+          <t>130862</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>202450</t>
+          <t>204806</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>300691</t>
+          <t>302277</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>115533</t>
+          <t>112826</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>203532</t>
+          <t>204619</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>101871</t>
+          <t>99311</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>146165</t>
+          <t>146653</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>230262</t>
+          <t>228472</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>331668</t>
+          <t>334671</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>58064</t>
+          <t>61214</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>116220</t>
+          <t>119010</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>72915</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>114303</t>
+          <t>112522</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>144085</t>
+          <t>146876</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>218736</t>
+          <t>216496</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>31410</t>
+          <t>31632</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>67931</t>
+          <t>69061</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>29763</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>59380</t>
+          <t>63149</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,47 +7705,47 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>90205</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>66438</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>116558</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>90205</t>
-        </is>
-      </c>
-      <c r="S65" s="2" t="inlineStr">
-        <is>
-          <t>66396</t>
-        </is>
-      </c>
-      <c r="T65" s="2" t="inlineStr">
-        <is>
-          <t>118320</t>
-        </is>
-      </c>
-      <c r="U65" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="V65" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>174167</t>
+          <t>179715</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>162101</t>
+          <t>169505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181512</t>
+          <t>187638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>122589</t>
+          <t>129852</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114147</t>
+          <t>123219</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128443</t>
+          <t>136033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>296755</t>
+          <t>309567</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284535</t>
+          <t>295625</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306691</t>
+          <t>320424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>21884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33787</t>
+          <t>31205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>817</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>12821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>15100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>21494</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>468</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>468</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>109385</t>
+          <t>115252</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90652</t>
+          <t>96759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131049</t>
+          <t>135222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70859</t>
+          <t>75570</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60256</t>
+          <t>62981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82939</t>
+          <t>88191</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>180244</t>
+          <t>190821</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156019</t>
+          <t>167258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201243</t>
+          <t>213529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34019</t>
+          <t>34014</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51836</t>
+          <t>53230</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33541</t>
+          <t>36031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>57509</t>
+          <t>59131</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77021</t>
+          <t>79240</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>36471</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54160</t>
+          <t>53385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20331</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48921</t>
+          <t>50272</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70145</t>
+          <t>70005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>51994</t>
+          <t>51957</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36751</t>
+          <t>36727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71517</t>
+          <t>70791</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33930</t>
+          <t>34791</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>26306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43892</t>
+          <t>45603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>85925</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68700</t>
+          <t>69174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106595</t>
+          <t>109921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18860</t>
+          <t>20786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27718</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39522</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15595</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8868</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26220</t>
+          <t>24412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57525</t>
+          <t>59244</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45784</t>
+          <t>47755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70165</t>
+          <t>71843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59085</t>
+          <t>59732</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50642</t>
+          <t>50525</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69108</t>
+          <t>69820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>116609</t>
+          <t>118976</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102192</t>
+          <t>103451</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>131986</t>
+          <t>135020</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33904</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>23966</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44355</t>
+          <t>44683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>21127</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>28759</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>54254</t>
+          <t>54041</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43245</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68831</t>
+          <t>67050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21055</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29689</t>
+          <t>30143</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20325</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24951</t>
+          <t>24753</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46091</t>
+          <t>44940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>24789</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12175</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18685</t>
+          <t>18263</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28438</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38245</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2777,22 +2777,22 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21200</t>
+          <t>21195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,27 +2837,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26585</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18994</t>
+          <t>19333</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36089</t>
+          <t>36505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13592</t>
+          <t>13755</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16038</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>92889</t>
+          <t>117241</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77353</t>
+          <t>96826</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109615</t>
+          <t>137928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>180805</t>
+          <t>92712</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>138769</t>
+          <t>78206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>220691</t>
+          <t>105954</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>273694</t>
+          <t>209953</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>227787</t>
+          <t>183471</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>329707</t>
+          <t>233834</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>21414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>51190</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28903</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47550</t>
+          <t>42778</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>51844</t>
+          <t>62946</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29902</t>
+          <t>48239</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72818</t>
+          <t>80055</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>29149</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>9233</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>31470</t>
+          <t>39724</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25564</t>
+          <t>30906</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>26172</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>26437</t>
+          <t>32869</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>42755</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15851</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36960</t>
+          <t>34969</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>36443</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>26692</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>56125</t>
+          <t>58431</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>28375</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>14149</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>13785</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>34979</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>167177</t>
+          <t>211399</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>167177</t>
+          <t>211399</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>167177</t>
+          <t>211399</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>257218</t>
+          <t>179498</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>257218</t>
+          <t>179498</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>257218</t>
+          <t>179498</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>424395</t>
+          <t>390897</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>424395</t>
+          <t>390897</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>424395</t>
+          <t>390897</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19635</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,27 +3940,27 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>22543</t>
+          <t>26470</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>36233</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>75741</t>
+          <t>89654</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>67261</t>
+          <t>78553</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>84365</t>
+          <t>99283</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>84397</t>
+          <t>92779</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>77415</t>
+          <t>84309</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>89994</t>
+          <t>99067</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>160138</t>
+          <t>182433</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>148667</t>
+          <t>170479</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>169523</t>
+          <t>194542</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>23042</t>
+          <t>25889</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31420</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>23949</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>455</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>51485</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>38732</t>
+          <t>41333</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>61368</t>
+          <t>63749</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>37493</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>46373</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>87322</t>
+          <t>89752</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>73230</t>
+          <t>76791</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>100177</t>
+          <t>103074</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>20516</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>28574</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11161</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>23275</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>37241</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>27929</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>47538</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23021</t>
+          <t>23233</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>23212</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>31725</t>
+          <t>31257</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>15565</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32426</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>50821</t>
+          <t>50968</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>28017</t>
+          <t>26948</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>25098</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>34913</t>
+          <t>33246</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>13257</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>482</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>134294</t>
+          <t>135330</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>134294</t>
+          <t>135330</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>134294</t>
+          <t>135330</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>220696</t>
+          <t>222685</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>220696</t>
+          <t>222685</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>220696</t>
+          <t>222685</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>170016</t>
+          <t>199403</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>146533</t>
+          <t>176835</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>188900</t>
+          <t>221470</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>177918</t>
+          <t>209154</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>161440</t>
+          <t>191211</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>192819</t>
+          <t>225240</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>347933</t>
+          <t>408556</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>318891</t>
+          <t>378881</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>373242</t>
+          <t>433461</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,76%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>85518</t>
+          <t>96872</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>66404</t>
+          <t>78469</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>110721</t>
+          <t>118626</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>53955</t>
+          <t>66381</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>52664</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>66870</t>
+          <t>79732</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,17 +5678,17 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>139473</t>
+          <t>163253</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>139791</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>170761</t>
+          <t>189970</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>23613</t>
+          <t>24443</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>14469</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>36561</t>
+          <t>38733</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>22771</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>54234</t>
+          <t>58412</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>26253</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>20278</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>38860</t>
+          <t>45990</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>24702</t>
+          <t>28315</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>34141</t>
+          <t>39315</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>50955</t>
+          <t>59533</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>37061</t>
+          <t>45305</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>65898</t>
+          <t>76048</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>28727</t>
+          <t>29616</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>32093</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>40862</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>28891</t>
+          <t>33753</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>53766</t>
+          <t>60096</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>13933</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>43192</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>306923</t>
+          <t>362990</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>306923</t>
+          <t>362990</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>306923</t>
+          <t>362990</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>641224</t>
+          <t>750504</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>641224</t>
+          <t>750504</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>641224</t>
+          <t>750504</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>442658</t>
+          <t>237813</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>314493</t>
+          <t>215658</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>549579</t>
+          <t>263993</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>115824</t>
+          <t>136521</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>101414</t>
+          <t>120520</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>130678</t>
+          <t>152745</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>558482</t>
+          <t>374334</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>420918</t>
+          <t>343391</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>739291</t>
+          <t>404384</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>115925</t>
+          <t>133227</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>47344</t>
+          <t>111421</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>199945</t>
+          <t>154461</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>80274</t>
+          <t>92080</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>67359</t>
+          <t>78238</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>94708</t>
+          <t>108722</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>196198</t>
+          <t>225308</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>88145</t>
+          <t>202030</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>278987</t>
+          <t>251094</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>27380</t>
+          <t>35785</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>25079</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>49413</t>
+          <t>49058</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,67 +6551,67 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>37908</t>
+          <t>45274</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>28819</t>
+          <t>34643</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>47598</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>81059</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>65974</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>99892</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
           <t>10,59%</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>65288</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>27697</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
-          <t>94777</t>
-        </is>
-      </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>22301</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>36692</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>18859</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>35964</t>
+          <t>41159</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>54913</t>
+          <t>55050</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>24823</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>25977</t>
+          <t>29919</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>20654</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>42907</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,17 +6925,17 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>35759</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>626117</t>
+          <t>452502</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>626117</t>
+          <t>452502</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>626117</t>
+          <t>452502</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>898128</t>
+          <t>765647</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>898128</t>
+          <t>765647</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>898128</t>
+          <t>765647</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7085,32 +7085,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1109519</t>
+          <t>976139</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>968866</t>
+          <t>927042</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1379152</t>
+          <t>1021654</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7120,32 +7120,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>774064</t>
+          <t>752290</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>721708</t>
+          <t>715871</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>883061</t>
+          <t>789502</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7155,32 +7155,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>1883584</t>
+          <t>1728429</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1735249</t>
+          <t>1668072</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2259673</t>
+          <t>1789019</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -7198,32 +7198,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>399600</t>
+          <t>450975</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>265924</t>
+          <t>412655</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>473770</t>
+          <t>497366</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7233,32 +7233,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>318053</t>
+          <t>354006</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>269935</t>
+          <t>323512</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>349112</t>
+          <t>382697</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,32 +7268,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>717653</t>
+          <t>804981</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>559840</t>
+          <t>757316</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>796708</t>
+          <t>857776</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -7311,32 +7311,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>147073</t>
+          <t>163774</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>97858</t>
+          <t>135920</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>185073</t>
+          <t>194477</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7346,32 +7346,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>113146</t>
+          <t>125988</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>91080</t>
+          <t>108817</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>130862</t>
+          <t>145936</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>260219</t>
+          <t>289762</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>204806</t>
+          <t>258054</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>302277</t>
+          <t>326101</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -7424,32 +7424,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>166908</t>
+          <t>181078</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>112826</t>
+          <t>155075</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>204619</t>
+          <t>213610</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7459,32 +7459,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>124273</t>
+          <t>136996</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>99311</t>
+          <t>118215</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>146653</t>
+          <t>157072</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>291181</t>
+          <t>318074</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>228472</t>
+          <t>286651</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>334671</t>
+          <t>356925</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -7537,32 +7537,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>92429</t>
+          <t>99594</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>61214</t>
+          <t>80100</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>119010</t>
+          <t>124873</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7572,32 +7572,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>93416</t>
+          <t>105357</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>72915</t>
+          <t>86200</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>125254</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>185845</t>
+          <t>204951</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>146876</t>
+          <t>176572</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>216496</t>
+          <t>232658</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7650,32 +7650,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>59829</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>69061</t>
+          <t>78461</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7685,32 +7685,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>39982</t>
+          <t>40529</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>29934</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>63149</t>
+          <t>52355</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>90205</t>
+          <t>100357</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>66438</t>
+          <t>82215</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>116558</t>
+          <t>125061</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -7763,17 +7763,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1965751</t>
+          <t>1931388</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1965751</t>
+          <t>1931388</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1965751</t>
+          <t>1931388</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1462935</t>
+          <t>1515166</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1462935</t>
+          <t>1515166</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1462935</t>
+          <t>1515166</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>3428686</t>
+          <t>3446554</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>3428686</t>
+          <t>3446554</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>3428686</t>
+          <t>3446554</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
